--- a/Docs/ISIS1225 - Tablas de Datos Lab 4.xlsx
+++ b/Docs/ISIS1225 - Tablas de Datos Lab 4.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniandes.sharepoint.com/sites/ISIS1225/Documentos compartidos/General/2025-10/Laboratorios/Lab 04 - Pilas y colas/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k.teranm\Downloads\LAB_0_EDA\Laboratorio-4-G08\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="120" documentId="13_ncr:1_{059725CA-9D74-4145-8FC3-28FE5756BBF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8CAB1D75-7132-4A69-A395-BC4C20E1FCBD}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E547F7A-9771-48BB-80D1-E16CB7644232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D82936D8-D2C9-4EB2-9CBC-3665F65B95FD}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{D82936D8-D2C9-4EB2-9CBC-3665F65B95FD}"/>
   </bookViews>
   <sheets>
     <sheet name="01-Data Lab 4" sheetId="1" r:id="rId1"/>
@@ -178,7 +178,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -194,11 +194,26 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -275,139 +290,6 @@
           <bgColor indexed="65"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Dax-Regular"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Dax-Regular"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Dax-Regular"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Dax-Regular"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Dax-Regular"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Dax-Regular"/>
-        <scheme val="none"/>
-      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -567,6 +449,139 @@
           <bgColor indexed="65"/>
         </patternFill>
       </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Dax-Regular"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Dax-Regular"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Dax-Regular"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Dax-Regular"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Dax-Regular"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Dax-Regular"/>
+        <scheme val="none"/>
+      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1330,6 +1345,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1337,7 +1353,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2007,6 +2022,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2014,7 +2030,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2684,6 +2699,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2691,7 +2707,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2891,10 +2906,10 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>'01-Data Lab 4'!$A$3:$A$10</c:f>
+              <c:f>'01-Data Lab 4'!$A$3:$A$11</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>5.0000000000000001E-3</c:v>
                 </c:pt>
@@ -2924,10 +2939,10 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'01-Data Lab 4'!$F$3:$F$10</c:f>
+              <c:f>'01-Data Lab 4'!$F$3:$F$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -3366,6 +3381,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3373,7 +3389,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3573,10 +3588,10 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>'01-Data Lab 4'!$A$3:$A$10</c:f>
+              <c:f>'01-Data Lab 4'!$A$3:$A$11</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>5.0000000000000001E-3</c:v>
                 </c:pt>
@@ -3606,10 +3621,10 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'01-Data Lab 4'!$G$3:$G$10</c:f>
+              <c:f>'01-Data Lab 4'!$G$3:$G$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -4048,6 +4063,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4055,7 +4071,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4255,10 +4270,10 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>'01-Data Lab 4'!$A$3:$A$10</c:f>
+              <c:f>'01-Data Lab 4'!$A$3:$A$11</c:f>
               <c:numCache>
                 <c:formatCode>0.00%</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
                 <c:pt idx="0">
                   <c:v>5.0000000000000001E-3</c:v>
                 </c:pt>
@@ -4288,10 +4303,10 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'01-Data Lab 4'!$H$3:$H$10</c:f>
+              <c:f>'01-Data Lab 4'!$H$3:$H$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
+                <c:ptCount val="9"/>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -4730,6 +4745,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4737,7 +4753,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -8167,7 +8182,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9305925" cy="6076950"/>
+    <xdr:ext cx="9296400" cy="6070600"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
@@ -8200,7 +8215,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9305925" cy="6076950"/>
+    <xdr:ext cx="9296400" cy="6070600"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
@@ -8233,7 +8248,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9305925" cy="6076950"/>
+    <xdr:ext cx="9296400" cy="6070600"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
@@ -8332,7 +8347,7 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:absoluteAnchor>
     <xdr:pos x="0" y="0"/>
-    <xdr:ext cx="9305925" cy="6076950"/>
+    <xdr:ext cx="8661400" cy="6286500"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
@@ -8362,8 +8377,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{072D0253-75B0-4C0B-8972-D03303899249}" name="Table1" displayName="Table1" ref="A2:H10" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
-  <autoFilter ref="A2:H10" xr:uid="{072D0253-75B0-4C0B-8972-D03303899249}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{072D0253-75B0-4C0B-8972-D03303899249}" name="Table1" displayName="Table1" ref="A2:H11" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
+  <autoFilter ref="A2:H11" xr:uid="{072D0253-75B0-4C0B-8972-D03303899249}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -8378,19 +8393,19 @@
     <tableColumn id="2" xr3:uid="{23CECC62-35E0-466E-9502-4F5CC2E6F7A7}" name="Tamaño de la muestra (ARRAY_LIST)" dataDxfId="16">
       <calculatedColumnFormula>Table1[[#This Row],[Porcentaje de la muestra '[pct']]]*10000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{19B1D273-887B-4392-991E-015D36D99E5B}" name="enqueue (Array List) " dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{56471E76-DCC6-4EED-8237-BCC256B57E91}" name="dequeue (Array List) " dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{61DF25D7-A2A3-4D39-B0C6-29804C1B33DB}" name="peek (Array List) " dataDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{092BA754-1EE8-42B8-A0C9-8E5FBAFE3FD2}" name="push (Array List)" dataDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{F7FD567A-4A42-4CDC-9449-A0BA8E9714D3}" name="pop (Array List)" dataDxfId="4"/>
-    <tableColumn id="11" xr3:uid="{91D17C3E-2CFC-4978-91FF-19ADDF3A1CD9}" name="top(Array List) " dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{19B1D273-887B-4392-991E-015D36D99E5B}" name="enqueue (Array List) " dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{56471E76-DCC6-4EED-8237-BCC256B57E91}" name="dequeue (Array List) " dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{61DF25D7-A2A3-4D39-B0C6-29804C1B33DB}" name="peek (Array List) " dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{092BA754-1EE8-42B8-A0C9-8E5FBAFE3FD2}" name="push (Array List)" dataDxfId="12"/>
+    <tableColumn id="9" xr3:uid="{F7FD567A-4A42-4CDC-9449-A0BA8E9714D3}" name="pop (Array List)" dataDxfId="11"/>
+    <tableColumn id="11" xr3:uid="{91D17C3E-2CFC-4978-91FF-19ADDF3A1CD9}" name="top(Array List) " dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C35EFFA4-2B65-46C5-8257-6884800B9577}" name="Table13" displayName="Table13" ref="A13:H21" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C35EFFA4-2B65-46C5-8257-6884800B9577}" name="Table13" displayName="Table13" ref="A13:H21" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
   <autoFilter ref="A13:H21" xr:uid="{5C24B5A8-1B8E-4092-B34A-66FF5413D106}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -8402,13 +8417,13 @@
     <filterColumn colId="7" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{16584851-71BC-4FF5-B248-C3F46BA653AF}" name="Porcentaje de la muestra [pct]" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{4F9B7329-040C-4D35-96E7-B9181424DC65}" name="Tamaño de la muestra (LINKED_LIST)" dataDxfId="12">
+    <tableColumn id="1" xr3:uid="{16584851-71BC-4FF5-B248-C3F46BA653AF}" name="Porcentaje de la muestra [pct]" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{4F9B7329-040C-4D35-96E7-B9181424DC65}" name="Tamaño de la muestra (LINKED_LIST)" dataDxfId="6">
       <calculatedColumnFormula>Table13[[#This Row],[Porcentaje de la muestra '[pct']]]*10000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{BDA028DF-4CED-4928-B040-96AD8F8A43EB}" name="enqueue (Linked List) " dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{A5E99D51-DD73-48A7-AE0D-601A8EE89AFA}" name="dequeue (Linked List)  " dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{EE99E4CD-A6F0-492B-B754-38221659D42F}" name="peek (Linked List)  " dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{BDA028DF-4CED-4928-B040-96AD8F8A43EB}" name="enqueue (Linked List) " dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{A5E99D51-DD73-48A7-AE0D-601A8EE89AFA}" name="dequeue (Linked List)  " dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{EE99E4CD-A6F0-492B-B754-38221659D42F}" name="peek (Linked List)  " dataDxfId="3"/>
     <tableColumn id="8" xr3:uid="{D4319BDE-1663-4E02-A459-D4E464B40376}" name="push (Linked List) " dataDxfId="2"/>
     <tableColumn id="9" xr3:uid="{D1102AA4-3669-4976-AB80-8CA1D8EED93A}" name="pop (Linked List) " dataDxfId="1"/>
     <tableColumn id="11" xr3:uid="{A75BD949-6BC0-4683-B105-18DE72DE82D5}" name="top(Linked List) " dataDxfId="0"/>
@@ -8715,28 +8730,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5B14742-4EBB-4241-AC8A-0E5F24F7BB7B}">
   <dimension ref="A1:H21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.81640625" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="19.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="24.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="24.42578125" style="6" customWidth="1"/>
-    <col min="6" max="12" width="24.42578125" customWidth="1"/>
+    <col min="1" max="1" width="19.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="24.453125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="24.453125" style="6" customWidth="1"/>
+    <col min="6" max="12" width="24.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.25" customHeight="1">
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="8" t="s">
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
     </row>
-    <row r="2" spans="1:8" s="5" customFormat="1" ht="30">
+    <row r="2" spans="1:8" s="5" customFormat="1" ht="28">
       <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
@@ -8762,7 +8777,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:8" s="5" customFormat="1">
+    <row r="3" spans="1:8" s="5" customFormat="1" ht="14">
       <c r="A3" s="2">
         <v>5.0000000000000001E-3</v>
       </c>
@@ -8777,7 +8792,7 @@
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
     </row>
-    <row r="4" spans="1:8" s="5" customFormat="1">
+    <row r="4" spans="1:8" s="5" customFormat="1" ht="14">
       <c r="A4" s="2">
         <v>0.05</v>
       </c>
@@ -8830,10 +8845,10 @@
         <f>Table1[[#This Row],[Porcentaje de la muestra '[pct']]]*10000</f>
         <v>3000</v>
       </c>
-      <c r="C7" s="4"/>
+      <c r="C7" s="7"/>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
+      <c r="F7" s="7"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
     </row>
@@ -8845,10 +8860,10 @@
         <f>Table1[[#This Row],[Porcentaje de la muestra '[pct']]]*10000</f>
         <v>5000</v>
       </c>
-      <c r="C8" s="4"/>
+      <c r="C8" s="7"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
+      <c r="F8" s="7"/>
       <c r="G8" s="4"/>
       <c r="H8" s="4"/>
     </row>
@@ -8860,10 +8875,10 @@
         <f>Table1[[#This Row],[Porcentaje de la muestra '[pct']]]*10000</f>
         <v>8000</v>
       </c>
-      <c r="C9" s="4"/>
+      <c r="C9" s="7"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
+      <c r="F9" s="7"/>
       <c r="G9" s="4"/>
       <c r="H9" s="4"/>
     </row>
@@ -8875,26 +8890,39 @@
         <f>Table1[[#This Row],[Porcentaje de la muestra '[pct']]]*10000</f>
         <v>10000</v>
       </c>
-      <c r="C10" s="4"/>
+      <c r="C10" s="7"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
+      <c r="F10" s="7"/>
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
     </row>
-    <row r="12" spans="1:8" ht="14.25" customHeight="1">
-      <c r="C12" s="7" t="s">
+    <row r="11" spans="1:8">
+      <c r="A11" s="10"/>
+      <c r="B11" s="11">
+        <f>Table1[[#This Row],[Porcentaje de la muestra '[pct']]]*10000</f>
         <v>0</v>
       </c>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="8" t="s">
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="4"/>
+    </row>
+    <row r="12" spans="1:8" ht="14.25" customHeight="1">
+      <c r="C12" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
     </row>
-    <row r="13" spans="1:8" s="5" customFormat="1" ht="30">
+    <row r="13" spans="1:8" s="5" customFormat="1" ht="28">
       <c r="A13" s="4" t="s">
         <v>2</v>
       </c>
@@ -8920,7 +8948,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:8" s="5" customFormat="1">
+    <row r="14" spans="1:8" s="5" customFormat="1" ht="14">
       <c r="A14" s="2">
         <v>5.0000000000000001E-3</v>
       </c>
@@ -8935,7 +8963,7 @@
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
     </row>
-    <row r="15" spans="1:8" s="5" customFormat="1">
+    <row r="15" spans="1:8" s="5" customFormat="1" ht="14">
       <c r="A15" s="2">
         <v>0.05</v>
       </c>
